--- a/it_forms/005_router_configuration_quiz--it_forms.xlsx
+++ b/it_forms/005_router_configuration_quiz--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>option 5</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_6</t>
+          <t>option 6</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_7</t>
+          <t>option 7</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_8</t>
+          <t>option 8</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_9</t>
+          <t>option 9</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_10</t>
+          <t>option 10</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_11</t>
+          <t>option 11</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_12</t>
+          <t>option 12</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_13</t>
+          <t>option 13</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_14</t>
+          <t>option 14</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_15</t>
+          <t>option 15</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_16</t>
+          <t>option 16</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_17</t>
+          <t>option 17</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_18</t>
+          <t>option 18</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_19</t>
+          <t>option 19</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_20</t>
+          <t>option 20</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_21</t>
+          <t>option 21</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_22</t>
+          <t>option 22</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_23</t>
+          <t>option 23</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option_24</t>
+          <t>option 24</t>
         </is>
       </c>
     </row>
